--- a/www/download/IND.gross_output.s.mv.WIOD16.xlsx
+++ b/www/download/IND.gross_output.s.mv.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21610.99</t>
+          <t>21609538763.6678</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20797.768</t>
+          <t>20790998560.3486</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21990.447</t>
+          <t>21984958689.4053</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23645.123</t>
+          <t>23640447033.4887</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25064.774</t>
+          <t>25058624202.2898</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>26052.099</t>
+          <t>26048841907.0201</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>26768.507</t>
+          <t>26763665445.8724</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>28572.485</t>
+          <t>28566502151.2689</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>28808.141</t>
+          <t>28808945276.1502</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>29000.507</t>
+          <t>28995276737.5755</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>30078.4</t>
+          <t>30068825410.7788</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>34460.538</t>
+          <t>34442745579.7196</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34146.365</t>
+          <t>34144097631.8587</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34223.998</t>
+          <t>34222044576.66</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33439.628</t>
+          <t>33444600381.7754</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8979.97</t>
+          <t>8979515255.57627</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8932.45</t>
+          <t>8932818125.43773</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8588.069</t>
+          <t>8586817446.83834</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9029.471</t>
+          <t>9027641585.74007</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9141.716</t>
+          <t>9140306848.5318</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>8889.778</t>
+          <t>8890323718.76196</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9303.272</t>
+          <t>9302835968.49902</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>9441.473</t>
+          <t>9435334244.39113</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>9743.645</t>
+          <t>9739723342.97523</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9416.018</t>
+          <t>9414119252.05768</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>9746.873</t>
+          <t>9743780824.13692</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10752.139</t>
+          <t>10748388542.162</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10728.875</t>
+          <t>10725380949.7469</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>11134.355</t>
+          <t>11132261962.5059</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>10525.853</t>
+          <t>10524221000.6253</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11258.782</t>
+          <t>11252094841.6469</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10842.564</t>
+          <t>10838604410.155</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10591.321</t>
+          <t>10585868863.5682</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>11327.443</t>
+          <t>11323199757.8648</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12172.604</t>
+          <t>12171511313.4245</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11855.878</t>
+          <t>11855719901.1541</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12870.871</t>
+          <t>12875146675.8982</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>13620.119</t>
+          <t>13617552563.867</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>14097.997</t>
+          <t>14096337226.7102</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>13041.867</t>
+          <t>13040657357.1831</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14572.746</t>
+          <t>14570824080.6534</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>17041.179</t>
+          <t>17038870811.0918</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>15664.244</t>
+          <t>15663188794.7639</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>15507.761</t>
+          <t>15508094566.379</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>16774.04</t>
+          <t>16783152233.724</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6876.819</t>
+          <t>6876726041.57303</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6808.014</t>
+          <t>6807671076.44856</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6776.129</t>
+          <t>6775743439.76748</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6769.24</t>
+          <t>6769042264.41259</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6929.893</t>
+          <t>6929790062.91447</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6833.004</t>
+          <t>6832973029.55764</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7253.318</t>
+          <t>7253000022.84737</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>7444.939</t>
+          <t>7444569985.45695</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7769.894</t>
+          <t>7769929230.44475</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7307.742</t>
+          <t>7307403604.88675</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6454.612</t>
+          <t>6454053538.08621</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>6527.76</t>
+          <t>6526927065.91489</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6285.33</t>
+          <t>6285013708.53705</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6324.419</t>
+          <t>6324374509.4223</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>6754.04</t>
+          <t>6754160801.09789</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>160614.011</t>
+          <t>160611930750.26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>156906.105</t>
+          <t>156896659680.804</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>163445.867</t>
+          <t>163433427056.063</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>169352.866</t>
+          <t>169352484706.492</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>176542.243</t>
+          <t>176541730721.455</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>181427.556</t>
+          <t>181423456518.138</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>178225.115</t>
+          <t>178216568503.911</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>179518.727</t>
+          <t>179509520546.793</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>187531.82</t>
+          <t>187520401554.099</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>179676.585</t>
+          <t>179667467809.805</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>184778.199</t>
+          <t>184759194465.345</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>186320.706</t>
+          <t>186294571890.689</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>184855.52</t>
+          <t>184846044233.685</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>187364.254</t>
+          <t>187362834805.517</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>189987.605</t>
+          <t>189988046083.894</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27957.486</t>
+          <t>27956577238.1311</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27205.487</t>
+          <t>27197629542.2909</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27313.251</t>
+          <t>27306370756.0518</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28624.388</t>
+          <t>28620195913.1861</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30184.244</t>
+          <t>30179026610.0389</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>30484.468</t>
+          <t>30480798173.4577</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>31297.423</t>
+          <t>31295923286.4115</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>30675.264</t>
+          <t>30669168268.3622</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30889.909</t>
+          <t>30884545265.1482</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>29448.211</t>
+          <t>29442962925.4966</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>31516.052</t>
+          <t>31507945921.7139</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>34196.706</t>
+          <t>34184852804.868</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>35025.258</t>
+          <t>35021532242.6107</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>33537.742</t>
+          <t>33537437360.7916</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>34052.101</t>
+          <t>34055284138.2398</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2071059.115</t>
+          <t>2070988312458.52</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2027749.379</t>
+          <t>2027541731647.35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2027948.036</t>
+          <t>2027720231538.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2075980.695</t>
+          <t>2075914706027.34</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2151509.272</t>
+          <t>2151404318607.03</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2256495.604</t>
+          <t>2256372916884.74</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2428086.633</t>
+          <t>2428032198361.37</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2527290.885</t>
+          <t>2527008145327.51</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2685750.325</t>
+          <t>2685415720816.95</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2852439.68</t>
+          <t>2852235648027.67</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2809953.338</t>
+          <t>2809638482886.83</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3122025.905</t>
+          <t>3121502793210.12</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3236448.452</t>
+          <t>3236183854790.26</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3283111.799</t>
+          <t>3283099622808.27</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3226896.522</t>
+          <t>3226995572700.66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>557.219</t>
+          <t>557212196.901193</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>646.947</t>
+          <t>646844067.317941</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>729.198</t>
+          <t>729083304.032584</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>765.563</t>
+          <t>765529147.301038</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>688.884</t>
+          <t>688874713.909797</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>674.669</t>
+          <t>674644916.024875</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>623.622</t>
+          <t>623586051.562227</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>662.343</t>
+          <t>662264686.479339</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>794.808</t>
+          <t>794778832.647694</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>695.143</t>
+          <t>695091799.767936</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>632.873</t>
+          <t>632793069.683062</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>617.869</t>
+          <t>617741301.448102</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>558.049</t>
+          <t>558022465.839628</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>531.535</t>
+          <t>531523940.189672</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>520.21</t>
+          <t>520212755.544632</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11257.758</t>
+          <t>11257617252.2575</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11015.456</t>
+          <t>11015142476.5008</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11229.144</t>
+          <t>11227605350.3231</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11340.269</t>
+          <t>11339072693.9233</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11538.251</t>
+          <t>11538351608.2744</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11759.565</t>
+          <t>11759270671.9504</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>12191.006</t>
+          <t>12190924927.7493</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>12607.212</t>
+          <t>12604386462.8351</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>12903.225</t>
+          <t>12901115397.9804</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11690.224</t>
+          <t>11685990246.3948</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>12088.646</t>
+          <t>12093964222.0478</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>13152.564</t>
+          <t>13149229426.0377</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>12328.74</t>
+          <t>12334469277.7656</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>12595.95</t>
+          <t>12590472727.1993</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>12626.779</t>
+          <t>12638810416.3263</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>78178.645</t>
+          <t>78127726566.0346</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>74981.878</t>
+          <t>75086699276.5211</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>72665.697</t>
+          <t>72572500687.0264</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>76973.109</t>
+          <t>76855857505.9659</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>78675.209</t>
+          <t>78814723292.2185</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>78710.999</t>
+          <t>78792825510.1913</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>83553.979</t>
+          <t>83534720416.9078</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>85665.267</t>
+          <t>85499831085.2261</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>86164.424</t>
+          <t>86121031319.2905</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>77612.887</t>
+          <t>77608429946.4606</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>80052.037</t>
+          <t>80044804219.1465</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>87533.564</t>
+          <t>87520609902.4461</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>82967.802</t>
+          <t>82961871662.7036</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>83806.494</t>
+          <t>83805364592.1863</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>82464.672</t>
+          <t>82467824459.5974</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6570.85</t>
+          <t>6570588188.40115</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6690.194</t>
+          <t>6689805032.66884</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6745.562</t>
+          <t>6744479330.37906</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7398.797</t>
+          <t>7397577931.72513</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7607.343</t>
+          <t>7605967124.91041</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7739.993</t>
+          <t>7741496410.79421</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7290.121</t>
+          <t>7289559454.20061</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7614.709</t>
+          <t>7612105552.79584</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>8104.414</t>
+          <t>8101567664.94727</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7110.884</t>
+          <t>7110107926.37437</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>6530.37</t>
+          <t>6529959230.77392</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>6829.501</t>
+          <t>6827232501.0354</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6715.798</t>
+          <t>6714511341.31478</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>7084.672</t>
+          <t>7084067848.55317</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>6853.431</t>
+          <t>6850879489.43208</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>38322.13</t>
+          <t>38314544036.2029</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38932.853</t>
+          <t>38924706195.1575</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41500.234</t>
+          <t>41492763073.8081</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42834.185</t>
+          <t>42828041574.2672</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44894.016</t>
+          <t>44889468423.7603</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46821.43</t>
+          <t>46820867821.9649</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49580.943</t>
+          <t>49581953211.1585</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>50562.082</t>
+          <t>50564829728.6382</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>50302.038</t>
+          <t>50300514818.8268</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>41836.951</t>
+          <t>41833236767.279</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>44698.752</t>
+          <t>44693977339.3388</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>47445.792</t>
+          <t>47448959368.7665</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>44980.368</t>
+          <t>44984470111.0056</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>43392.507</t>
+          <t>43393836439.0171</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>43961.238</t>
+          <t>43961487696.0317</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1288.663</t>
+          <t>1288473932.61622</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1289.543</t>
+          <t>1289258197.38648</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1400.325</t>
+          <t>1399964432.55288</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1507.658</t>
+          <t>1506992900.10402</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1482.128</t>
+          <t>1481589497.26981</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1487.14</t>
+          <t>1486902534.56833</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1671.939</t>
+          <t>1671216513.76816</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1636.016</t>
+          <t>1635709778.04063</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1613.994</t>
+          <t>1613607713.69948</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1249.822</t>
+          <t>1249608877.48907</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1236.458</t>
+          <t>1236231991.87915</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1507.63</t>
+          <t>1506969280.59547</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1453.256</t>
+          <t>1452973108.45081</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1423.515</t>
+          <t>1423671778.43405</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1476.796</t>
+          <t>1476995656.09478</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6786.705</t>
+          <t>6774069639.21388</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6595.712</t>
+          <t>6585749239.32306</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6638.788</t>
+          <t>6632339257.63202</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7146.042</t>
+          <t>7144374651.09527</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7374.652</t>
+          <t>7371615224.73656</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7593.568</t>
+          <t>7597379565.89764</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7872.528</t>
+          <t>7880155485.86231</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7952.548</t>
+          <t>7948632296.80047</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>8588.333</t>
+          <t>8583959741.32965</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6449.92</t>
+          <t>6451246111.01363</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6385.312</t>
+          <t>6384001353.92694</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>6711.782</t>
+          <t>6709810435.58911</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6572.398</t>
+          <t>6569463081.19678</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6338.944</t>
+          <t>6339867550.78732</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6104.179</t>
+          <t>6105088738.01219</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>46483.444</t>
+          <t>46474152139.3086</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>45661.444</t>
+          <t>45652810596.6853</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>44757.307</t>
+          <t>44750290935.9167</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>46825.718</t>
+          <t>46821639462.5757</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50016.414</t>
+          <t>50015283743.5912</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>50211.829</t>
+          <t>50204300674.6048</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>51228.355</t>
+          <t>51221301529.8962</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>52340.881</t>
+          <t>52328166013.4042</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>53256.369</t>
+          <t>53244317667.0064</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>50438.75</t>
+          <t>50431060144.6107</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>49250.502</t>
+          <t>49244646785.0234</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>54656.043</t>
+          <t>54651176105.0416</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>51138.873</t>
+          <t>51142271548.0997</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>49086.517</t>
+          <t>49092753385.9767</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>48477.493</t>
+          <t>48487675798.1752</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>46451.482</t>
+          <t>46443272661.1098</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>46184.029</t>
+          <t>46171897642.1074</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>46390.289</t>
+          <t>46379621819.1592</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47256.045</t>
+          <t>47250465833.9118</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>48136.853</t>
+          <t>48130307756.8626</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>49116.754</t>
+          <t>49113509577.6742</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>49701.477</t>
+          <t>49698541681.8339</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>48611.915</t>
+          <t>48605670887.5999</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>46587.308</t>
+          <t>46581696377.8232</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>46824.306</t>
+          <t>46823241897.2574</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>47453.278</t>
+          <t>47446091992.8357</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>50438.265</t>
+          <t>50431557903.2587</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>51937.711</t>
+          <t>51932734617.5361</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>53714.401</t>
+          <t>53723951080.7163</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>50723.096</t>
+          <t>50723497488.0992</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8318.716</t>
+          <t>8318946719.51216</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8152.208</t>
+          <t>8151126368.39072</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7925.622</t>
+          <t>7924233264.70403</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8148.436</t>
+          <t>8147847456.86537</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7899.596</t>
+          <t>7898670017.35487</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8574.16</t>
+          <t>8575308523.91725</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8841.652</t>
+          <t>8841023825.50706</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9100.526</t>
+          <t>9099908404.18058</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>8780.883</t>
+          <t>8779354440.15689</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8473.293</t>
+          <t>8472324945.68901</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>7691.174</t>
+          <t>7689882927.4262</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>7468.977</t>
+          <t>7467864740.24912</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6654.112</t>
+          <t>6653743434.54132</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>6825.378</t>
+          <t>6823455129.33112</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7174.205</t>
+          <t>7173883404.09946</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10852.418</t>
+          <t>10851335469.5955</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10725.497</t>
+          <t>10723263156.0312</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10810.678</t>
+          <t>10807504367.8531</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10631.393</t>
+          <t>10629350037.7584</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10463.944</t>
+          <t>10462374680.1655</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10381.258</t>
+          <t>10380100210.7231</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>10501.07</t>
+          <t>10499923839.0396</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10279.994</t>
+          <t>10275374955.4287</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>10010.646</t>
+          <t>10010051380.7472</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9324.705</t>
+          <t>9324236384.76808</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>8706.525</t>
+          <t>8704089609.20302</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>8916.442</t>
+          <t>8913235717.31457</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>8218.747</t>
+          <t>8217610551.81153</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>8176.603</t>
+          <t>8176658291.43953</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>8897.61</t>
+          <t>8898464415.45085</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>162120.298</t>
+          <t>162117655841.498</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>170025.762</t>
+          <t>170020213123.887</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>182921.881</t>
+          <t>182916486463.042</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>200682.613</t>
+          <t>200679102953.581</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>199587.141</t>
+          <t>199580378943.182</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>178754.606</t>
+          <t>178749919108.338</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>176796.6</t>
+          <t>176793910295.378</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>183240.95</t>
+          <t>183237100821.146</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>187707.083</t>
+          <t>187697954678.573</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>196664.375</t>
+          <t>196659371129.233</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>200049.932</t>
+          <t>200039787796.104</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>201148.805</t>
+          <t>201134169241.38</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>218269.753</t>
+          <t>218263615876.686</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>238073.602</t>
+          <t>238070935317.153</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>262824.622</t>
+          <t>262828496222.359</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1249024.231</t>
+          <t>1248990082833.54</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1279284.897</t>
+          <t>1279187735779.35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1319770.406</t>
+          <t>1319708023199.65</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1396292.597</t>
+          <t>1396273202903.67</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1435081.517</t>
+          <t>1435054078163.99</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1420297.732</t>
+          <t>1420267382108.86</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1410996.457</t>
+          <t>1410943206075.58</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1413235.59</t>
+          <t>1413162410875.16</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1400121.588</t>
+          <t>1400108606209.37</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1415091.274</t>
+          <t>1415043950293.68</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1429135.544</t>
+          <t>1429046238785.83</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1449690.345</t>
+          <t>1449575893300.01</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1615118.585</t>
+          <t>1615071828508.48</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1769913.439</t>
+          <t>1769901065411.15</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1892788.504</t>
+          <t>1892826345604.95</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4025.151</t>
+          <t>4024666701.94069</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4599.33</t>
+          <t>4597937247.51561</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4583.766</t>
+          <t>4582456038.9703</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5076.083</t>
+          <t>5075020321.61917</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5290.409</t>
+          <t>5288896037.30494</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>5820.437</t>
+          <t>5819421858.03676</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6348.538</t>
+          <t>6348331492.97885</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6049.528</t>
+          <t>6046608200.97881</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5591.839</t>
+          <t>5590930408.74161</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5205.993</t>
+          <t>5205463087.76813</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>3838.202</t>
+          <t>3837166956.3402</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>4488.818</t>
+          <t>4487193927.88604</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>4346.297</t>
+          <t>4345728441.97872</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>4811.275</t>
+          <t>4811109792.77799</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>4787.345</t>
+          <t>4788190354.09005</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>57386.568</t>
+          <t>57381080682.1164</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>57046.776</t>
+          <t>57046837537.975</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>56706.19</t>
+          <t>56691352401.5449</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58474.886</t>
+          <t>58465236262.737</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>61120.938</t>
+          <t>61114214918.3844</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>60788.936</t>
+          <t>60786784776.6433</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>64928.591</t>
+          <t>64925922607.9222</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>64661.419</t>
+          <t>64655584213.9407</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>65194.909</t>
+          <t>65196519275.1371</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>56578.123</t>
+          <t>56568394111.327</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>60811.676</t>
+          <t>60810128359.3861</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>65923.151</t>
+          <t>65917051164.6911</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>59194.135</t>
+          <t>59195605651.9123</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>56853.877</t>
+          <t>56860544837.6838</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>56363.405</t>
+          <t>56372667335.3362</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>199434.221</t>
+          <t>199498030036.284</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>189782.347</t>
+          <t>189372301563.967</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>182298.076</t>
+          <t>181909112336.32</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>188773.688</t>
+          <t>188462668201.806</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>196162.802</t>
+          <t>195845757089.566</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>195320.756</t>
+          <t>195025137370.367</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>198845.132</t>
+          <t>199176122454.615</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>193192.315</t>
+          <t>193107685889.201</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>199806.412</t>
+          <t>199670945213.005</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>177338.015</t>
+          <t>177617158331.847</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>184190.677</t>
+          <t>184190367419.304</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>204612.514</t>
+          <t>204238227035.992</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>203104.568</t>
+          <t>202754012004.448</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>191019.567</t>
+          <t>190877223520.441</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>188109.056</t>
+          <t>187794268987.903</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>74286.722</t>
+          <t>74285382909.4333</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>71976.085</t>
+          <t>71924513692.1612</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>74334.171</t>
+          <t>74279627088.2245</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>77529.433</t>
+          <t>77514368608.1514</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>84144.958</t>
+          <t>84116096746.0388</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>83662.509</t>
+          <t>83626848717.1339</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>89863.821</t>
+          <t>89863890787.1741</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>86749.974</t>
+          <t>86689568321.152</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>90924.344</t>
+          <t>90883996406.0912</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>87386.635</t>
+          <t>87374798915.8748</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>90763.059</t>
+          <t>90732197610.1912</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>105945.19</t>
+          <t>105889871569.085</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>105853.328</t>
+          <t>105822229404.098</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>109006.422</t>
+          <t>109008224502.316</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>110538.935</t>
+          <t>110545444246.159</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3239.897</t>
+          <t>3240162377.03284</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3124.066</t>
+          <t>3123785885.02472</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3163.735</t>
+          <t>3163338668.15825</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3265.421</t>
+          <t>3266042692.61942</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3058.904</t>
+          <t>3059169563.51483</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3143.944</t>
+          <t>3143357214.11777</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3157.531</t>
+          <t>3156638075.10212</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3037.33</t>
+          <t>3036589858.95397</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3163.674</t>
+          <t>3163686144.86702</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2613.786</t>
+          <t>2614408486.43364</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2456.067</t>
+          <t>2456049054.77158</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2612.015</t>
+          <t>2611894353.37754</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2630.328</t>
+          <t>2631720009.42049</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2618.17</t>
+          <t>2619478547.00459</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2981.422</t>
+          <t>2981846143.99412</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>428.739</t>
+          <t>428645578.163094</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>448.488</t>
+          <t>448410990.533151</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>440.588</t>
+          <t>440451099.200796</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>477.912</t>
+          <t>477765324.11535</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>519.177</t>
+          <t>519033115.389385</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>521.483</t>
+          <t>521556402.848561</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>559.275</t>
+          <t>559256164.658585</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>583.017</t>
+          <t>582657475.553029</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>659.208</t>
+          <t>659102315.799573</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>635.932</t>
+          <t>635871317.889415</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>706.406</t>
+          <t>706205088.579532</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>690.143</t>
+          <t>689700105.485118</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>683.93</t>
+          <t>683783052.25547</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>622.339</t>
+          <t>622268759.702016</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>640.824</t>
+          <t>641011501.009062</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2149.848</t>
+          <t>2149721212.61615</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2199.587</t>
+          <t>2199352528.27906</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2187.453</t>
+          <t>2187296008.00287</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2297.286</t>
+          <t>2297252888.4386</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2211.875</t>
+          <t>2211808516.44365</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2235.748</t>
+          <t>2235673153.25166</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2466.482</t>
+          <t>2466275897.31241</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2446.104</t>
+          <t>2445819144.4433</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2434.457</t>
+          <t>2434443684.23871</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1872.696</t>
+          <t>1872610391.93686</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1707.733</t>
+          <t>1707397533.58216</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1883.878</t>
+          <t>1883316152.64434</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1974.695</t>
+          <t>1974572745.8614</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1935.881</t>
+          <t>1935877171.70861</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1997.102</t>
+          <t>1997222799.4843</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>76063.501</t>
+          <t>76061295362.1832</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>74978.157</t>
+          <t>74966556992.956</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>74644.033</t>
+          <t>74631780457.8012</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>75030.433</t>
+          <t>75026272624.9447</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>77985.678</t>
+          <t>77980673830.7013</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>77965.015</t>
+          <t>77958801541.6197</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>81550.897</t>
+          <t>81546841433.0344</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>82531.618</t>
+          <t>82517357892.6018</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>82522.877</t>
+          <t>82516507407.884</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>78665.003</t>
+          <t>78661304021.0754</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>81012.14</t>
+          <t>81003544651.1985</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>82200.415</t>
+          <t>82186818002.2328</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>84224.075</t>
+          <t>84218654215.6551</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>84195.039</t>
+          <t>84193579777.3679</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>84614.762</t>
+          <t>84615591527.1686</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>344.393</t>
+          <t>344374812.683157</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>313.032</t>
+          <t>312968728.72803</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>297.283</t>
+          <t>297214837.27335</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>324.475</t>
+          <t>324448280.175637</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>302.741</t>
+          <t>302712852.564131</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>302.461</t>
+          <t>302435220.935199</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>307.826</t>
+          <t>307825438.164213</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>325.752</t>
+          <t>325647809.009202</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>387.901</t>
+          <t>387811949.529857</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>350.609</t>
+          <t>350580046.52176</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>363.03</t>
+          <t>362969484.800659</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>329.691</t>
+          <t>329590094.532172</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>344.425</t>
+          <t>344377828.345991</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>333.612</t>
+          <t>333607833.134414</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>304.638</t>
+          <t>304662878.143173</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>19040.825</t>
+          <t>19040682811.0859</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19985.371</t>
+          <t>19984075764.484</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20773.454</t>
+          <t>20771063488.7641</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>25244.764</t>
+          <t>25243666885.6993</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>23990.593</t>
+          <t>23991048228.482</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>23442.3</t>
+          <t>23442113298.1514</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>23777.881</t>
+          <t>23777397587.3485</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>24589.287</t>
+          <t>24586017795.294</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>26748.361</t>
+          <t>26746340792.9422</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>28822.326</t>
+          <t>28823938933.8462</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>29804.992</t>
+          <t>29795672439.7553</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>31729.883</t>
+          <t>31720812595.2765</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>29834.984</t>
+          <t>29829153267.6334</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>33929.876</t>
+          <t>33925341065.7395</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>34007.727</t>
+          <t>34014734947.789</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>33750.295</t>
+          <t>33749424958.4133</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>34594.954</t>
+          <t>34593100181.5548</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>31648.578</t>
+          <t>31646415145.3217</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>31666.728</t>
+          <t>31665085882.1287</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>32421.205</t>
+          <t>32420822902.3688</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>33160.93</t>
+          <t>33160448926.8559</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>34281.138</t>
+          <t>34279975477.5909</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>35807.874</t>
+          <t>35804520863.525</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>37669.205</t>
+          <t>37667988454.7018</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>36455.098</t>
+          <t>36453875210.5583</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>37474.727</t>
+          <t>37470889854.8724</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>39193.447</t>
+          <t>39188491819.4921</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>37940.84</t>
+          <t>37938986068.1364</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>37971.611</t>
+          <t>37971929065.4575</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>38218.247</t>
+          <t>38220789699.8079</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14026.61</t>
+          <t>14026008269.4673</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13831.187</t>
+          <t>13830147759.6931</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>13516.389</t>
+          <t>13515031828.9284</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13404.107</t>
+          <t>13403454338.414</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>13832.174</t>
+          <t>13831944163.7326</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13074.048</t>
+          <t>13073744410.5435</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>13124.006</t>
+          <t>13123452065.9803</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>13210.415</t>
+          <t>13209480779.7794</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>13418.515</t>
+          <t>13417457293.3444</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>11542.177</t>
+          <t>11541431344.9511</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>11403.49</t>
+          <t>11401741940.1164</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12027.679</t>
+          <t>12025498592.8751</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11144.634</t>
+          <t>11143882088.4233</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>11211.214</t>
+          <t>11211122171.4747</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>11411.288</t>
+          <t>11412149176.2764</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>33634.822</t>
+          <t>33634468070.3527</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>32784.755</t>
+          <t>32783832232.1269</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>27376.326</t>
+          <t>27375152975.7614</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27904.437</t>
+          <t>27903946959.1981</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>26403.587</t>
+          <t>26403251745.2372</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>26141.405</t>
+          <t>26140900157.9718</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>25240.109</t>
+          <t>25238234376.831</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>25830.541</t>
+          <t>25828401210.2654</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>25287.108</t>
+          <t>25288666304.6498</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>24528.653</t>
+          <t>24527780722.4604</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>23154.66</t>
+          <t>23152668007.2258</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>23500.08</t>
+          <t>23498042369.122</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>18121.984</t>
+          <t>18121406119.2553</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>18063.239</t>
+          <t>18063044043.7328</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>18184.318</t>
+          <t>18184664895.9023</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>158393.773</t>
+          <t>158390576495.053</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>158486.666</t>
+          <t>158463029228.886</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>155881.96</t>
+          <t>155860425670.173</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>158003.526</t>
+          <t>157998742516.547</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>151889.552</t>
+          <t>151880443654.725</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>155065.262</t>
+          <t>155058242181.226</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>153985.616</t>
+          <t>153973669647.667</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>154148.048</t>
+          <t>154132963545.921</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>144935.907</t>
+          <t>144935804316.612</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>138909.145</t>
+          <t>138899429446.223</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>140394.951</t>
+          <t>140370291485.231</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>140108.613</t>
+          <t>140079428225.502</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>143654.52</t>
+          <t>143643794913.822</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>138107.476</t>
+          <t>138108469179.355</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>128984.343</t>
+          <t>128991411187.391</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4608.211</t>
+          <t>4608195569.77742</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4604.776</t>
+          <t>4603822530.17359</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4549.374</t>
+          <t>4548724011.00306</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4631.658</t>
+          <t>4633847714.48055</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4709.672</t>
+          <t>4710682177.81283</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4812.199</t>
+          <t>4812121262.19187</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5274.019</t>
+          <t>5274597526.21944</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>5578.699</t>
+          <t>5581776089.41722</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5707.804</t>
+          <t>5707699878.60704</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5659.673</t>
+          <t>5659299402.86449</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>5350.436</t>
+          <t>5349044006.69889</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>5917.614</t>
+          <t>5915728927.85524</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>5752.929</t>
+          <t>5752561751.29652</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>5847.994</t>
+          <t>5847899146.89606</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>5944.163</t>
+          <t>5944496703.15979</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2065.576</t>
+          <t>2065537663.3476</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2063.32</t>
+          <t>2063711810.05999</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2067.554</t>
+          <t>2067570666.1368</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2127.72</t>
+          <t>2127781919.61943</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2322.279</t>
+          <t>2322702386.98454</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2274.758</t>
+          <t>2275303987.79518</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2324.454</t>
+          <t>2324355041.76355</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2357.134</t>
+          <t>2356228837.4695</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2397.226</t>
+          <t>2396352794.00852</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2171.944</t>
+          <t>2171290069.87409</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2163.341</t>
+          <t>2162461324.96558</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2249.367</t>
+          <t>2248337285.78125</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2087.254</t>
+          <t>2086677130.28076</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2020.276</t>
+          <t>2020275580.87956</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2052.192</t>
+          <t>2052397508.36737</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9731.542</t>
+          <t>9729619094.01994</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>9199.535</t>
+          <t>9194578266.1579</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9040.398</t>
+          <t>9036317099.17284</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>9358.92</t>
+          <t>9356158145.44916</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>9974.81</t>
+          <t>9971710832.35328</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10125.868</t>
+          <t>10123730611.091</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>10208.558</t>
+          <t>10207200298.3239</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>10259.024</t>
+          <t>10251582593.7707</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>10438.949</t>
+          <t>10436492424.5415</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>9289.064</t>
+          <t>9287997746.33024</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>9576.947</t>
+          <t>9573302191.47967</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10331.371</t>
+          <t>10326084742.1356</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>9914.805</t>
+          <t>9913285344.25218</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>9929.628</t>
+          <t>9928974814.8286</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>9807.023</t>
+          <t>9809394704.44358</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>66861.202</t>
+          <t>66855969073.9131</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>63617.06</t>
+          <t>63607217271.9181</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>59901.262</t>
+          <t>59891124385.3653</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>60758.672</t>
+          <t>60760469151.2521</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>63665.363</t>
+          <t>63662177409.0751</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>63541.612</t>
+          <t>63539941042.8009</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>62525.036</t>
+          <t>62520747900.2735</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>61665.672</t>
+          <t>61653909875.4153</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>61703.958</t>
+          <t>61697714318.8504</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>58349.147</t>
+          <t>58341030907.9925</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>64166.555</t>
+          <t>64147243819.0025</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>68936.069</t>
+          <t>68906497878.9165</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>70302.258</t>
+          <t>70288324104.5988</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>74866.841</t>
+          <t>74864626791.8275</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>81786.402</t>
+          <t>81791618750.1199</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50310.319</t>
+          <t>50302694347.8039</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>45542.621</t>
+          <t>45511268026.4656</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>48126.025</t>
+          <t>48091894037.0436</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>51167.487</t>
+          <t>51151725145.181</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>56382.533</t>
+          <t>56354533570.1335</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>56243.163</t>
+          <t>56221559085.4337</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>58235.921</t>
+          <t>58246006559.8578</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>57594.04</t>
+          <t>57554019763.5685</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>57245.782</t>
+          <t>57214073604.7685</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>50293.077</t>
+          <t>50288873375.2349</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>56740.112</t>
+          <t>56725366751.1895</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>60078.166</t>
+          <t>60049402071.2122</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>59053.763</t>
+          <t>59038048736.3338</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>59248.559</t>
+          <t>59250196166.3495</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>61709.083</t>
+          <t>61709956974.0617</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>279819.374</t>
+          <t>279777087206.538</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>263033.544</t>
+          <t>262881598090.888</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>261346.943</t>
+          <t>261223916456.266</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>263265.32</t>
+          <t>263192535715.348</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>274623.781</t>
+          <t>274523794505.827</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>287294.928</t>
+          <t>287234913908.474</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>292910.514</t>
+          <t>292871547463.141</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>279152.76</t>
+          <t>279010576531.701</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>276124.958</t>
+          <t>276061980844.672</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>232119.324</t>
+          <t>232068116603.564</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>238036.544</t>
+          <t>237905514035.675</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>259656.313</t>
+          <t>259470191486.849</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>261581.919</t>
+          <t>261526383888.639</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>256878.437</t>
+          <t>256865402078.882</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>264321.02</t>
+          <t>264375916935.438</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2575755.568</t>
+          <t>2575730603353.02</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2624857.49</t>
+          <t>2624714683855.6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2794971.317</t>
+          <t>2794855978692.23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2908591.885</t>
+          <t>2908506966635.87</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>3000494.641</t>
+          <t>3000337536772.91</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>3149706.911</t>
+          <t>3149535728895.15</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3292823.966</t>
+          <t>3292708248510.7</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3305531.961</t>
+          <t>3305428730331.72</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3401263.291</t>
+          <t>3401180004097.76</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3501719.759</t>
+          <t>3501593341422.3</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>3496785.781</t>
+          <t>3496560198653.37</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>3667927.15</t>
+          <t>3667617027422.46</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>3936326.315</t>
+          <t>3936264189263.31</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>4121844.364</t>
+          <t>4121825177276.58</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>4283346.951</t>
+          <t>4283454105582.91</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7658947.361</t>
+          <t>7658701411332.19</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7654874.728</t>
+          <t>7653746850571.07</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7866338.425</t>
+          <t>7865084820221.58</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8168590.894</t>
+          <t>8167820014677.31</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8425170.968</t>
+          <t>8424474937217.13</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8667951.658</t>
+          <t>8667252287930.69</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>9007104.07</t>
+          <t>9007113120862.78</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>9115315.465</t>
+          <t>9114223855183.56</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>9373798.993</t>
+          <t>9372974072963.83</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>9523696.172</t>
+          <t>9523443858599.99</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>9540839.098</t>
+          <t>9539870767126.89</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>10158770.256</t>
+          <t>10156949520857.8</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>10698797.383</t>
+          <t>10697898472633.5</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>11094375.661</t>
+          <t>11094179741318.1</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>11354272.667</t>
+          <t>11354351157171.2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2986.708</t>
+          <t>2986665720.73569</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2927.801</t>
+          <t>2927609795.61264</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3036.426</t>
+          <t>3036097527.9833</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>3028.853</t>
+          <t>3028789832.38502</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>3204.879</t>
+          <t>3204816808.70155</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3121.824</t>
+          <t>3121818894.97323</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>3193.371</t>
+          <t>3193264269.11651</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>3231.585</t>
+          <t>3231200343.55448</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>3387.849</t>
+          <t>3387551294.97671</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3168.019</t>
+          <t>3167801232.50436</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>3049.486</t>
+          <t>3049030804.50615</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>3019.204</t>
+          <t>3018515489.34046</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2854.184</t>
+          <t>2854043535.93157</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2801.254</t>
+          <t>2801152740.35365</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2776.058</t>
+          <t>2776153324.22854</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>11056.571</t>
+          <t>11053137668.1052</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10672.277</t>
+          <t>10668134626.2113</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>10526.886</t>
+          <t>10523469891.7541</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>10777.033</t>
+          <t>10773405586.6338</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>10517.03</t>
+          <t>10514231645.4202</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>10913.449</t>
+          <t>10913376335.5066</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>11370.433</t>
+          <t>11368554457.739</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>11201.406</t>
+          <t>11195048562.9459</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>11643.453</t>
+          <t>11643952731.1567</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>11121.539</t>
+          <t>11120885393.066</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10785.911</t>
+          <t>10782512558.8694</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12444.015</t>
+          <t>12437132914.1425</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>12373.467</t>
+          <t>12371390919.8334</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>12531.619</t>
+          <t>12530893182.4509</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>12616.335</t>
+          <t>12619839923.8194</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4977.193</t>
+          <t>4977008532.53529</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4777.318</t>
+          <t>4776011769.93664</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4781.985</t>
+          <t>4780696134.17952</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4878.519</t>
+          <t>4877590703.22698</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>4950.69</t>
+          <t>4949886187.5391</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>5109.623</t>
+          <t>5109390909.23057</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>5146.068</t>
+          <t>5145403756.01119</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>5506.037</t>
+          <t>5504694617.99188</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>5614.162</t>
+          <t>5613892052.07377</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>5107.29</t>
+          <t>5106745892.85579</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>5090.553</t>
+          <t>5089226645.02314</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>5522.959</t>
+          <t>5521067503.15223</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>5429.506</t>
+          <t>5428964210.91954</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>5559.204</t>
+          <t>5559029189.48371</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>5447.408</t>
+          <t>5447921599.9914</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
